--- a/extended_database/PCS_database_manikin-human_Jun.xlsx
+++ b/extended_database/PCS_database_manikin-human_Jun.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="10" documentId="8_{6D431D33-B1FE-4917-AC0C-5376EACB926E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79071803-438B-4F03-ABAE-9EF896A7B0B0}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="24496" windowHeight="15675" tabRatio="821" activeTab="2" xr2:uid="{090EAD7F-58B7-4F22-A372-29ECDC5D8A3D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="24496" windowHeight="15675" tabRatio="821" activeTab="1" xr2:uid="{090EAD7F-58B7-4F22-A372-29ECDC5D8A3D}"/>
   </bookViews>
   <sheets>
     <sheet name="PCS_database_manikin_info" sheetId="3" r:id="rId1"/>
